--- a/public/hcqha-class-list-template.xlsx
+++ b/public/hcqha-class-list-template.xlsx
@@ -1,69 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Classes" sheetId="1" r:id="rId1"/>
-    <sheet name="Options" sheetId="2" r:id="rId2"/>
-    <sheet name="Notes" sheetId="3" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Options" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="3">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF555555"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FF555555"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -100,16 +77,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="TableStyleMedium4"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -434,544 +478,663 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.83203125" customWidth="1"/>
-    <col min="2" max="2" width="24.83203125" customWidth="1"/>
-    <col min="3" max="3" width="9.83203125" customWidth="1"/>
-    <col min="4" max="4" width="34.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" customWidth="1"/>
-    <col min="6" max="6" width="18.83203125" customWidth="1"/>
-    <col min="7" max="7" width="24.83203125" customWidth="1"/>
-    <col min="8" max="8" width="18.83203125" customWidth="1"/>
-    <col min="9" max="9" width="20.83203125" customWidth="1"/>
+    <col width="24.83203125" customWidth="1" min="1" max="1"/>
+    <col width="24.83203125" customWidth="1" min="2" max="2"/>
+    <col width="9.83203125" customWidth="1" min="3" max="3"/>
+    <col width="34.83203125" customWidth="1" min="4" max="4"/>
+    <col width="18.83203125" customWidth="1" min="5" max="5"/>
+    <col width="18.83203125" customWidth="1" min="6" max="6"/>
+    <col width="24.83203125" customWidth="1" min="7" max="7"/>
+    <col width="18.83203125" customWidth="1" min="8" max="8"/>
+    <col width="20.83203125" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="str">
-        <v>Category</v>
-      </c>
-      <c r="B1" s="1" t="str">
-        <v>Break Before</v>
-      </c>
-      <c r="C1" s="1" t="str">
-        <v>Class #</v>
-      </c>
-      <c r="D1" s="1" t="str">
-        <v>Class Name</v>
-      </c>
-      <c r="E1" s="1" t="str">
-        <v>Judge 1</v>
-      </c>
-      <c r="F1" s="1" t="str">
-        <v>Judge 2</v>
-      </c>
-      <c r="G1" s="1" t="str">
-        <v>Break After</v>
-      </c>
-      <c r="H1" s="1" t="str">
-        <v>Type</v>
-      </c>
-      <c r="I1" s="1" t="str">
-        <v>HP Category</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Break Before</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Class #</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Class Name</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Judge 1</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Judge 2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Break After</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>HP Category</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="str">
-        <v>Quarter Horse Halter</v>
-      </c>
-      <c r="B2" s="3" t="str">
-        <v/>
-      </c>
-      <c r="C2" s="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Quarter Horse Halter</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="str"/>
+      <c r="C2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="str">
-        <v>QH Gelding 4 yrs &amp; over</v>
-      </c>
-      <c r="E2" s="2" t="str">
-        <v>Connie Barry</v>
-      </c>
-      <c r="F2" s="2" t="str">
-        <v>Robyn Smith</v>
-      </c>
-      <c r="G2" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H2" s="3" t="str">
-        <v>Placing</v>
-      </c>
-      <c r="I2" s="3" t="str">
-        <v>Overall Halter</v>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>QH Gelding 4 yrs &amp; over</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Connie Barry</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Robyn Smith</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="str"/>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Placing</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Overall Halter</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="str">
-        <v>Trail</v>
-      </c>
-      <c r="B3" s="3" t="str">
-        <v>SET UP TRAIL</v>
-      </c>
-      <c r="C3" s="2">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Trail</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>SET UP TRAIL</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="str">
-        <v>Junior Horse Trail</v>
-      </c>
-      <c r="E3" s="2" t="str">
-        <v>Connie Barry</v>
-      </c>
-      <c r="F3" s="2" t="str">
-        <v>Robyn Smith</v>
-      </c>
-      <c r="G3" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H3" s="3" t="str">
-        <v>Score</v>
-      </c>
-      <c r="I3" s="3" t="str">
-        <v>Junior Horse</v>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Junior Horse Trail</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Connie Barry</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Robyn Smith</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="str"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Junior Horse</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="str">
-        <v>Showmanship</v>
-      </c>
-      <c r="B4" s="3" t="str">
-        <v/>
-      </c>
-      <c r="C4" s="2">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Showmanship</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="str"/>
+      <c r="C4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D4" s="2" t="str">
-        <v>Amateur Showmanship</v>
-      </c>
-      <c r="E4" s="2" t="str">
-        <v>Connie Barry</v>
-      </c>
-      <c r="F4" s="2" t="str">
-        <v>Robyn Smith</v>
-      </c>
-      <c r="G4" s="3" t="str">
-        <v>BREAK FOR GEAR CHANGE</v>
-      </c>
-      <c r="H4" s="3" t="str">
-        <v>Class Only</v>
-      </c>
-      <c r="I4" s="3" t="str">
-        <v>Amateur</v>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Amateur Showmanship</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Connie Barry</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Robyn Smith</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>BREAK FOR GEAR CHANGE</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Class Only</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Amateur</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="str">
-        <v>Ranch Riding</v>
-      </c>
-      <c r="B5" s="3" t="str">
-        <v/>
-      </c>
-      <c r="C5" s="2">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Ranch Riding</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="str"/>
+      <c r="C5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="2" t="str">
-        <v>Senior Horse Ranch Riding</v>
-      </c>
-      <c r="E5" s="2" t="str">
-        <v>Connie Barry</v>
-      </c>
-      <c r="F5" s="2" t="str">
-        <v>Robyn Smith</v>
-      </c>
-      <c r="G5" s="3" t="str">
-        <v/>
-      </c>
-      <c r="H5" s="3" t="str">
-        <v>TBC (draw)</v>
-      </c>
-      <c r="I5" s="3" t="str">
-        <v>Senior Horse</v>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Senior Horse Ranch Riding</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Connie Barry</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Robyn Smith</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="str"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>TBC (draw)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Senior Horse</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="str">
-        <v>Western Pleasure</v>
-      </c>
-      <c r="B6" s="3" t="str">
-        <v/>
-      </c>
-      <c r="C6" s="2">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Western Pleasure</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="str"/>
+      <c r="C6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="2" t="str">
-        <v>Beginner Western Pleasure</v>
-      </c>
-      <c r="E6" s="2" t="str">
-        <v>Connie Barry</v>
-      </c>
-      <c r="F6" s="2" t="str">
-        <v>Robyn Smith</v>
-      </c>
-      <c r="G6" s="3" t="str">
-        <v>BREAK AND OPEN PEN</v>
-      </c>
-      <c r="H6" s="3" t="str">
-        <v>TBC (whole class)</v>
-      </c>
-      <c r="I6" s="3" t="str">
-        <v>Beginner</v>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Beginner Western Pleasure</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Connie Barry</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Robyn Smith</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>BREAK AND OPEN PEN</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>TBC (whole class)</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="str">
-        <v>Reining</v>
-      </c>
-      <c r="B7" s="3" t="str">
-        <v/>
-      </c>
-      <c r="C7" s="2">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Reining</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="str"/>
+      <c r="C7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D7" s="2" t="str">
-        <v>Youth Reining</v>
-      </c>
-      <c r="E7" s="2" t="str">
-        <v>Connie Barry</v>
-      </c>
-      <c r="F7" s="2" t="str">
-        <v>Robyn Smith</v>
-      </c>
-      <c r="G7" s="3" t="str">
-        <v>FINISH</v>
-      </c>
-      <c r="H7" s="3" t="str">
-        <v>Score</v>
-      </c>
-      <c r="I7" s="3" t="str">
-        <v>Youth</v>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Youth Reining</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Connie Barry</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Robyn Smith</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>FINISH</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Youth</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A2:A200">
+    <dataValidation sqref="A2:A200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>Options!$A$2:$A$17</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B200 G2:G200">
+    <dataValidation sqref="B2:B200 G2:G200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>Options!$B$2:$B$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H2:H200">
+    <dataValidation sqref="H2:H200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>Options!$C$2:$C$6</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I2:I200">
+    <dataValidation sqref="I2:I200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>Options!$D$2:$D$13</formula1>
     </dataValidation>
   </dataValidations>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I7"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="28.83203125" customWidth="1"/>
-    <col min="2" max="2" width="28.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-    <col min="4" max="4" width="24.83203125" customWidth="1"/>
+    <col width="28.83203125" customWidth="1" min="1" max="1"/>
+    <col width="28.83203125" customWidth="1" min="2" max="2"/>
+    <col width="22.83203125" customWidth="1" min="3" max="3"/>
+    <col width="24.83203125" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="str">
-        <v>Program Categories</v>
-      </c>
-      <c r="B1" s="1" t="str">
-        <v>Break Labels</v>
-      </c>
-      <c r="C1" s="1" t="str">
-        <v>Scoring Types</v>
-      </c>
-      <c r="D1" s="1" t="str">
-        <v>High Points Categories</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Program Categories</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Break Labels</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Scoring Types</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>High Points Categories</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>Quarter Horse Halter</v>
-      </c>
-      <c r="B2" t="str">
-        <v>SET UP TRAIL</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Score</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Overall Halter</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Quarter Horse Halter</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SET UP TRAIL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Overall Halter</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>Paint Halter</v>
-      </c>
-      <c r="B3" t="str">
-        <v>BREAK FOR GEAR CHANGE</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Placing</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Overall 2YO</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Paint Halter</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BREAK FOR GEAR CHANGE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Placing</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Overall 2YO</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>Paint Bred Halter</v>
-      </c>
-      <c r="B4" t="str">
-        <v>BREAK AND OPEN PEN</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Class Only</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Overall 3YO</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Paint Bred Halter</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BREAK AND OPEN PEN</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Class Only</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Overall 3YO</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>Appaloosa Halter</v>
-      </c>
-      <c r="B5" t="str">
-        <v>FINISH</v>
-      </c>
-      <c r="C5" t="str">
-        <v>TBC (draw)</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Junior Horse</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Appaloosa Halter</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>FINISH</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TBC (draw)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Junior Horse</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>Other Breeds Halter</v>
-      </c>
-      <c r="B6" t="str">
-        <v/>
-      </c>
-      <c r="C6" t="str">
-        <v>TBC (whole class)</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Senior Horse</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Other Breeds Halter</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TBC (whole class)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Senior Horse</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v>Showmanship</v>
-      </c>
-      <c r="B7" t="str">
-        <v/>
-      </c>
-      <c r="C7" t="str">
-        <v/>
-      </c>
-      <c r="D7" t="str">
-        <v>Amateur</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Showmanship</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Amateur</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
-        <v>Lungeline</v>
-      </c>
-      <c r="B8" t="str">
-        <v/>
-      </c>
-      <c r="C8" t="str">
-        <v/>
-      </c>
-      <c r="D8" t="str">
-        <v>Novice Amateur</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Lungeline</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Novice Amateur</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
-        <v>Hunter in Hand</v>
-      </c>
-      <c r="B9" t="str">
-        <v/>
-      </c>
-      <c r="C9" t="str">
-        <v/>
-      </c>
-      <c r="D9" t="str">
-        <v>Select</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Hunter in Hand</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Select</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
-        <v>Hack</v>
-      </c>
-      <c r="B10" t="str">
-        <v/>
-      </c>
-      <c r="C10" t="str">
-        <v/>
-      </c>
-      <c r="D10" t="str">
-        <v>Beginner</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Hack</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Beginner</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
-        <v>Hunter Under Saddle</v>
-      </c>
-      <c r="B11" t="str">
-        <v/>
-      </c>
-      <c r="C11" t="str">
-        <v/>
-      </c>
-      <c r="D11" t="str">
-        <v>EWD</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Hunter Under Saddle</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Improver</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
-        <v>Hunt Seat Equitation</v>
-      </c>
-      <c r="B12" t="str">
-        <v/>
-      </c>
-      <c r="C12" t="str">
-        <v/>
-      </c>
-      <c r="D12" t="str">
-        <v>Youth</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Hunt Seat Equitation</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EWD</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="str">
-        <v>Trail</v>
-      </c>
-      <c r="B13" t="str">
-        <v/>
-      </c>
-      <c r="C13" t="str">
-        <v/>
-      </c>
-      <c r="D13" t="str">
-        <v>Leadline</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Trail</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Youth</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
-        <v>Western Pleasure</v>
-      </c>
-      <c r="B14" t="str">
-        <v/>
-      </c>
-      <c r="C14" t="str">
-        <v/>
-      </c>
-      <c r="D14" t="str">
-        <v/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Western Pleasure</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Leadline</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="str">
-        <v>Horsemanship</v>
-      </c>
-      <c r="B15" t="str">
-        <v/>
-      </c>
-      <c r="C15" t="str">
-        <v/>
-      </c>
-      <c r="D15" t="str">
-        <v/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Horsemanship</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="str">
-        <v>Ranch Riding</v>
-      </c>
-      <c r="B16" t="str">
-        <v/>
-      </c>
-      <c r="C16" t="str">
-        <v/>
-      </c>
-      <c r="D16" t="str">
-        <v/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ranch on the Rail</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="str">
-        <v>Reining</v>
-      </c>
-      <c r="B17" t="str">
-        <v/>
-      </c>
-      <c r="C17" t="str">
-        <v/>
-      </c>
-      <c r="D17" t="str">
-        <v/>
-      </c>
-    </row>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ranch Riding</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Reining</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D17"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="115.83203125" customWidth="1"/>
+    <col width="115.83203125" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="str">
-        <v>How to use this template</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>How to use this template</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="str">
-        <v>Delete the example rows on the Classes tab and add your own classes underneath the same headers.</v>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Delete the example rows on the Classes tab and add your own classes underneath the same headers.</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="str">
-        <v>Grey cells are free-entry examples: class number, class name, Judge 1, and Judge 2.</v>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Grey cells are free-entry examples: class number, class name, Judge 1, and Judge 2.</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="str">
-        <v>Option columns can use the values shown on the Options tab. The importer also accepts blank Break and HP Category cells.</v>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Option columns can use the values shown on the Options tab. The importer also accepts blank Break and HP Category cells.</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="str">
-        <v>Scoring Type options: Score, Placing, Class Only, TBC (draw), and TBC (whole class).</v>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Scoring Type options: Score, Placing, Class Only, TBC (draw), and TBC (whole class).</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="str">
-        <v>Break labels are optional banners shown before or after a class, e.g. SET UP TRAIL or FINISH.</v>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Break labels are optional banners shown before or after a class, e.g. SET UP TRAIL or FINISH.</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="str">
-        <v>Duplicate class names are okay when the class number or category is different.</v>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Duplicate class names are okay when the class number or category is different.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A7"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>